--- a/project/excel/nist_sp_800_171.xlsx
+++ b/project/excel/nist_sp_800_171.xlsx
@@ -7,26 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP800171Document" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CatalogBody" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Metadata" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Role" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Party" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Address" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ResponsibleParty" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BackMatter" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Resource" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Citation" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ResourceLink" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="IdentifiedElement" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ControlGroup" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Control" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Parameter" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ParameterSelection" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Guideline" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Property" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Link" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Part" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Sp800171Publication" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sp800171Family" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sp800171Requirement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sp800171RequirementItem" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sp800171Parameter" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sp800171AssessmentObjective" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sp800171AssessmentMethod" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sp800171Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,423 +420,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>catalog</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>href</t>
+          <t>sp800171_revision</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>media-type</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>controls</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>usage</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>guidelines</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>select</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>how-many</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"one,one-or-more"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>prose</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>href</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>rel</t>
+          <t>requirement_families</t>
         </is>
       </c>
     </row>
@@ -869,82 +452,26 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>family_number</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>back-matter</t>
+          <t>family_requirements</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>prose</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"security_requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -955,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,51 +493,76 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>last-modified</t>
+          <t>requirement_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>requirement_status</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>oscal-version</t>
+          <t>incorporated_into_requirements</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>props</t>
+          <t>addressed_by_requirements</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>links</t>
+          <t>requirement_statement</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>requirement_items</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>parties</t>
+          <t>requirement_discussion</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>responsible-parties</t>
+          <t>requirement_parameters</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>requirement_objectives</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>requirement_methods</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>requirement_references</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>source_controls</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"withdrawn"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1021,18 +573,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>requirement_item_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>requirement_item_text</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>requirement_subitems</t>
         </is>
       </c>
     </row>
@@ -1053,36 +610,41 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>odp_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>odp_label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>odp_usage</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>short-name</t>
+          <t>odp_guideline</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>email-addresses</t>
+          <t>odp_choices</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>addresses</t>
+          <t>odp_selection_count</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"one,one_or_more"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1093,28 +655,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>addr-lines</t>
+          <t>requirement_objective_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>requirement_determination</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>postal-code</t>
+          <t>assessed_requirement_item</t>
         </is>
       </c>
     </row>
@@ -1135,16 +692,21 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>role-id</t>
+          <t>requirement_method_kind</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>party-uuids</t>
+          <t>requirement_method_objects</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"examine,interview,test"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1155,54 +717,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>resources</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>uuid</t>
+          <t>cited_publication</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>cited_publication_citation</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rlinks</t>
+          <t>cited_publication_url</t>
         </is>
       </c>
     </row>

--- a/project/excel/nist_sp_800_171.xlsx
+++ b/project/excel/nist_sp_800_171.xlsx
@@ -452,17 +452,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>family_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>family_number</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/project/excel/nist_sp_800_171.xlsx
+++ b/project/excel/nist_sp_800_171.xlsx
@@ -7,26 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP800171Document" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CatalogBody" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Metadata" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Role" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Party" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Address" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ResponsibleParty" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BackMatter" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Resource" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Citation" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ResourceLink" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="IdentifiedElement" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ControlGroup" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Control" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Parameter" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ParameterSelection" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Guideline" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Property" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Link" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Part" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Sp800171Publication" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sp800171Family" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sp800171Requirement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sp800171RequirementItem" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sp800171Parameter" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sp800171AssessmentObjective" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sp800171AssessmentMethod" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sp800171Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,423 +420,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>catalog</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>href</t>
+          <t>sp800171_revision</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>media-type</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>controls</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>usage</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>guidelines</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>select</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"family,requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>how-many</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"one,one-or-more"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>prose</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>href</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>rel</t>
+          <t>requirement_families</t>
         </is>
       </c>
     </row>
@@ -869,82 +452,26 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>family_number</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>back-matter</t>
+          <t>family_requirements</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>_class</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>prose</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>props</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>parts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"security_requirement"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -955,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,51 +493,76 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>last-modified</t>
+          <t>requirement_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>requirement_status</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>oscal-version</t>
+          <t>incorporated_into_requirements</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>props</t>
+          <t>addressed_by_requirements</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>links</t>
+          <t>requirement_statement</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>requirement_items</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>parties</t>
+          <t>requirement_discussion</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>responsible-parties</t>
+          <t>requirement_parameters</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>requirement_objectives</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>requirement_methods</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>requirement_references</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>source_controls</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"withdrawn"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1021,18 +573,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>requirement_item_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>requirement_item_text</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>requirement_subitems</t>
         </is>
       </c>
     </row>
@@ -1053,36 +610,41 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>odp_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>odp_label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>odp_usage</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>short-name</t>
+          <t>odp_guideline</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>email-addresses</t>
+          <t>odp_choices</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>addresses</t>
+          <t>odp_selection_count</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"one,one_or_more"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1093,28 +655,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>addr-lines</t>
+          <t>requirement_objective_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>requirement_determination</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>postal-code</t>
+          <t>assessed_requirement_item</t>
         </is>
       </c>
     </row>
@@ -1135,16 +692,21 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>role-id</t>
+          <t>requirement_method_kind</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>party-uuids</t>
+          <t>requirement_method_objects</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"examine,interview,test"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1155,54 +717,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>resources</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>uuid</t>
+          <t>cited_publication</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>cited_publication_citation</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rlinks</t>
+          <t>cited_publication_url</t>
         </is>
       </c>
     </row>
